--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11071.58</v>
+        <v>10780.03</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>13119.85</v>
+        <v>12774.36</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>18938.51</v>
+        <v>18439.8</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12294.67</v>
+        <v>12071.71</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>26544.56</v>
+        <v>26063.17</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8865.83</v>
+        <v>8628.43</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>23656.13</v>
+        <v>23022.7</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11935.38</v>
+        <v>11970.13</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11330.62</v>
+        <v>11426.78</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>32806.19</v>
+        <v>32751.34</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>65320.08</v>
+        <v>65210.86</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>18531.92</v>
+        <v>18500.94</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>34691.83</v>
+        <v>34633.82</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7628.05</v>
+        <v>7615.3</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>19906.5</v>
+        <v>20151.49</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>31124.47</v>
+        <v>31507.52</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6484.91</v>
+        <v>6564.73</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>14930.82</v>
+        <v>15114.58</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>19312.01</v>
+        <v>19549.68</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7133.58</v>
+        <v>7221.37</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7505.32</v>
+        <v>7605.24</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>59736.47</v>
+        <v>60531.72</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>27373.62</v>
+        <v>27738.04</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8795.98</v>
+        <v>8913.08</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>22833.17</v>
+        <v>23137.14</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>65304.87</v>
+        <v>66174.25</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>79667.35000000001</v>
+        <v>80706.98</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>29469.44</v>
+        <v>29854.01</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7825.47</v>
+        <v>7927.59</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>29699.76</v>
+        <v>30430.67</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>13064.96</v>
+        <v>13386.49</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7628.05</v>
+        <v>7772.32</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>56588.09</v>
+        <v>57658.32</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>33191.39</v>
+        <v>33568.85</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>14239.64</v>
+        <v>14401.58</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>32207.31</v>
+        <v>32497.45</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>27741.91</v>
+        <v>27919.34</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6493.13</v>
+        <v>6534.66</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7639.57</v>
+        <v>7688.43</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>13623.68</v>
+        <v>13666.54</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>8810.559999999999</v>
+        <v>8838.280000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16441.35</v>
+        <v>16493.08</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>69664.99000000001</v>
+        <v>69953.73</v>
       </c>
     </row>
     <row r="45">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>6483.89</v>
+        <v>6456.04</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
@@ -688,7 +688,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -749,7 +753,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +879,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +944,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1070,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1135,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1261,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1326,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1391,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1456,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1521,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1647,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1712,11 @@
           <t>77.367.722-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1777,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1842,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1907,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1972,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2098,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2285,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2350,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2415,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2480,11 @@
           <t>77.547.481-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2545,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2610,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2797,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2862,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2927,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +2992,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3057,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3122,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3187,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3193,7 +3317,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2026.xlsx
@@ -2582,7 +2582,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
